--- a/artfynd/A 61611-2022 artfynd.xlsx
+++ b/artfynd/A 61611-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 61611-2022 artfynd.xlsx
+++ b/artfynd/A 61611-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,63 +675,49 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>61831950</v>
+        <v>106271268</v>
       </c>
       <c r="B2" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Trytebergen NO, Dls</t>
+          <t>Hökedalsbeget, Dls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>348048.6244489476</v>
+        <v>347931</v>
       </c>
       <c r="R2" t="n">
-        <v>6536556.930191442</v>
+        <v>6536639</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -755,27 +741,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2016-10-20</t>
+          <t>2023-02-01</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2016-10-20</t>
+          <t>2023-02-01</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>På Asp</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,27 +771,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anders Niklasson</t>
+          <t>Samuel Sjöberg</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anders Niklasson</t>
+          <t>Samuel Sjöberg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>106271268</v>
+        <v>106272821</v>
       </c>
       <c r="B3" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -836,17 +812,19 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Hökedalsbeget, Dls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>347931.7846844943</v>
+        <v>347926</v>
       </c>
       <c r="R3" t="n">
-        <v>6536638.521026925</v>
+        <v>6536644</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -876,54 +854,40 @@
           <t>2023-02-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>12:21</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-02-01</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>12:21</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Samuel Sjöberg</t>
+          <t>Christine Bryngelsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Samuel Sjöberg</t>
+          <t>Christine Bryngelsson, Samuel Sjöberg, Samuel Sjöberg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>106264501</v>
+        <v>61831950</v>
       </c>
       <c r="B4" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -948,23 +912,30 @@
           <t>(L.) Hoffm.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Grandalen, Dls</t>
+          <t>Trytebergen NO, Dls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>348052.6563037646</v>
+        <v>348049</v>
       </c>
       <c r="R4" t="n">
-        <v>6536554.187895576</v>
+        <v>6536557</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -988,22 +959,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-02-01</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-10-20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-02-01</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-10-20</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På Asp</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1012,71 +978,50 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Christine Bryngelsson</t>
+          <t>Anders Niklasson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Christine Bryngelsson, Samuel Sjöberg</t>
+          <t>Anders Niklasson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>106272821</v>
+        <v>106264501</v>
       </c>
       <c r="B5" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1085,14 +1030,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hökedalsbeget, Dls</t>
+          <t>Grandalen, Dls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>347926.8011696063</v>
+        <v>348053</v>
       </c>
       <c r="R5" t="n">
-        <v>6536643.367393551</v>
+        <v>6536554</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1122,19 +1067,9 @@
           <t>2023-02-01</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-02-01</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1147,6 +1082,21 @@
       <c r="AG5" t="b">
         <v>0</v>
       </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
@@ -1155,10 +1105,108 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Christine Bryngelsson, Samuel Sjöberg, Samuel Sjöberg</t>
+          <t>Christine Bryngelsson, Samuel Sjöberg</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>106264841</v>
+      </c>
+      <c r="B6" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Grandalen, Dls</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>348119</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6536505</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Tisselskog</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2023-02-01</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2023-02-01</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Christine Bryngelsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Christine Bryngelsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 61611-2022 artfynd.xlsx
+++ b/artfynd/A 61611-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -780,6 +785,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106271268</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -881,6 +891,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106272821</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61831950</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1109,6 +1129,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106264501</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,8 +1232,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106264841</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>